--- a/9回目プログラム/out.xlsx
+++ b/9回目プログラム/out.xlsx
@@ -1294,13 +1294,13 @@
       <c r="H10" s="109" t="n"/>
       <c r="I10" s="110" t="inlineStr">
         <is>
-          <t>トートバッグ</t>
+          <t>財布</t>
         </is>
       </c>
       <c r="J10" s="107" t="n"/>
       <c r="K10" s="110" t="inlineStr">
         <is>
-          <t>参考書が3冊入っている水色</t>
+          <t>折り畳みの財布赤</t>
         </is>
       </c>
       <c r="L10" s="106" t="n"/>
@@ -1310,13 +1310,13 @@
       <c r="P10" s="99" t="n"/>
       <c r="Q10" s="112" t="inlineStr">
         <is>
-          <t>04/06 09:04</t>
+          <t>06/07 10:52</t>
         </is>
       </c>
       <c r="R10" s="99" t="n"/>
       <c r="S10" s="111" t="inlineStr">
         <is>
-          <t>体育館</t>
+          <t>4301教室</t>
         </is>
       </c>
     </row>
@@ -1398,13 +1398,13 @@
       <c r="H14" s="109" t="n"/>
       <c r="I14" s="110" t="inlineStr">
         <is>
-          <t>ネックレスシルバー製</t>
+          <t xml:space="preserve">コート　</t>
         </is>
       </c>
       <c r="J14" s="107" t="n"/>
       <c r="K14" s="110" t="inlineStr">
         <is>
-          <t>シルバーのネックレス銀</t>
+          <t>ボタンがついている茶</t>
         </is>
       </c>
       <c r="L14" s="106" t="n"/>
@@ -1414,13 +1414,13 @@
       <c r="P14" s="99" t="n"/>
       <c r="Q14" s="112" t="inlineStr">
         <is>
-          <t>04/15 07:03</t>
+          <t>06/11 10:52</t>
         </is>
       </c>
       <c r="R14" s="99" t="n"/>
       <c r="S14" s="111" t="inlineStr">
         <is>
-          <t>7403教室</t>
+          <t>食堂</t>
         </is>
       </c>
     </row>
@@ -1502,13 +1502,13 @@
       <c r="H18" s="109" t="n"/>
       <c r="I18" s="110" t="inlineStr">
         <is>
-          <t>ボストンバッグ</t>
+          <t>スマホ</t>
         </is>
       </c>
       <c r="J18" s="107" t="n"/>
       <c r="K18" s="110" t="inlineStr">
         <is>
-          <t>白</t>
+          <t>iPhone13黒</t>
         </is>
       </c>
       <c r="L18" s="106" t="n"/>
@@ -1518,13 +1518,13 @@
       <c r="P18" s="99" t="n"/>
       <c r="Q18" s="112" t="inlineStr">
         <is>
-          <t>03/24 20:50</t>
+          <t>06/13 10:57</t>
         </is>
       </c>
       <c r="R18" s="99" t="n"/>
       <c r="S18" s="111" t="inlineStr">
         <is>
-          <t>バスロータリー</t>
+          <t>7101教室</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,24 @@
       <c r="A22" s="97" t="n"/>
       <c r="B22" s="109" t="n"/>
       <c r="C22" s="109" t="n"/>
-      <c r="D22" s="109" t="n"/>
-      <c r="E22" s="109" t="n"/>
-      <c r="F22" s="109" t="n"/>
+      <c r="D22" s="109" t="inlineStr">
+        <is>
+          <t>¥</t>
+        </is>
+      </c>
+      <c r="E22" s="109" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G22" s="109" t="inlineStr">
         <is>
-          <t>¥</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H22" s="109" t="inlineStr">
@@ -1626,13 +1638,13 @@
       <c r="P22" s="99" t="n"/>
       <c r="Q22" s="112" t="inlineStr">
         <is>
-          <t>05/13 13:41</t>
+          <t>06/06 10:57</t>
         </is>
       </c>
       <c r="R22" s="99" t="n"/>
       <c r="S22" s="111" t="inlineStr">
         <is>
-          <t>3107教室</t>
+          <t>1101教室</t>
         </is>
       </c>
     </row>
